--- a/data/trans_dic/IP36A-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP36A-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adultos que perciben algun tipo de pensión</t>
+          <t>Adultos que perciben algun tipo de pensión (tasa de respuesta: 99,16%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,18; 37,14</t>
+          <t>5,35; 37,76</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,59</t>
+          <t>0,0; 18,98</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,81</t>
+          <t>0,0; 23,66</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,34</t>
+          <t>0,0; 29,09</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,33; 30,06</t>
+          <t>3,3; 27,46</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,91</t>
+          <t>0,0; 21,16</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,12; 40,35</t>
+          <t>7,54; 41,02</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,32; 46,76</t>
+          <t>7,4; 47,84</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,77; 24,71</t>
+          <t>6,06; 25,62</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,71; 15,42</t>
+          <t>1,7; 15,73</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6,1; 25,89</t>
+          <t>5,71; 26,02</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8,66; 34,46</t>
+          <t>6,79; 31,84</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,97</t>
+          <t>0,0; 15,5</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,01; 19,83</t>
+          <t>2,04; 19,57</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,49; 21,04</t>
+          <t>4,44; 21,11</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,71; 31,77</t>
+          <t>3,75; 31,42</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,28</t>
+          <t>0,0; 11,83</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,68; 21,66</t>
+          <t>4,74; 21,62</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,92; 26,45</t>
+          <t>6,94; 27,24</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,27; 41,16</t>
+          <t>7,27; 40,96</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,02; 9,64</t>
+          <t>1,01; 10,06</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5,38; 16,19</t>
+          <t>5,23; 16,6</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7,46; 21,04</t>
+          <t>7,62; 19,96</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,06; 29,52</t>
+          <t>8,12; 29,87</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,87; 36,33</t>
+          <t>3,87; 34,83</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,5; 27,28</t>
+          <t>6,68; 28,36</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,66; 34,6</t>
+          <t>8,61; 34,46</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11,06; 54,23</t>
+          <t>12,57; 56,21</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,89; 29,78</t>
+          <t>6,91; 31,25</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,74; 21,11</t>
+          <t>4,94; 22,96</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,75; 29,65</t>
+          <t>5,74; 30,07</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13,68; 56,21</t>
+          <t>13,48; 53,7</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7,44; 25,62</t>
+          <t>8,43; 26,02</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7,53; 20,56</t>
+          <t>7,35; 21,01</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10,06; 26,91</t>
+          <t>10,25; 28,3</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>17,33; 47,51</t>
+          <t>19,27; 48,83</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,83; 13,02</t>
+          <t>3,08; 12,86</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,87; 19,42</t>
+          <t>8,46; 18,55</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,16; 16,57</t>
+          <t>6,96; 16,35</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,31; 17,35</t>
+          <t>3,34; 16,57</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,3; 14,35</t>
+          <t>4,23; 15,27</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,19; 18,55</t>
+          <t>8,24; 18,35</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,41; 22,71</t>
+          <t>10,25; 22,27</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,07; 19,18</t>
+          <t>5,88; 20,25</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,37; 11,35</t>
+          <t>4,49; 11,65</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9,7; 17,11</t>
+          <t>9,62; 16,71</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9,88; 17,37</t>
+          <t>9,98; 17,74</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,37; 15,46</t>
+          <t>5,47; 14,78</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,2; 13,72</t>
+          <t>2,37; 13,59</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,0; 16,12</t>
+          <t>6,32; 16,34</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,09; 13,66</t>
+          <t>3,83; 12,85</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22,41; 47,54</t>
+          <t>21,14; 48,35</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,17; 11,29</t>
+          <t>1,16; 10,64</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,4; 16,56</t>
+          <t>6,0; 17,49</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,56; 17,82</t>
+          <t>5,99; 17,53</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>19,38; 39,68</t>
+          <t>19,51; 40,01</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,88; 10,27</t>
+          <t>2,87; 10,47</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7,21; 14,27</t>
+          <t>7,17; 15,11</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6,24; 13,44</t>
+          <t>6,24; 13,32</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>23,02; 40,24</t>
+          <t>22,93; 39,94</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,81; 14,41</t>
+          <t>3,74; 14,85</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,43; 14,24</t>
+          <t>1,42; 13,04</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,82</t>
+          <t>0,0; 6,16</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6,29; 22,51</t>
+          <t>6,16; 21,58</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3,27; 12,65</t>
+          <t>2,96; 13,68</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,5; 14,85</t>
+          <t>3,59; 14,38</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,2; 12,81</t>
+          <t>2,12; 12,88</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4,55; 18,32</t>
+          <t>4,75; 17,92</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4,58; 11,86</t>
+          <t>4,47; 11,26</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3,54; 11,45</t>
+          <t>3,6; 10,93</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1,32; 7,63</t>
+          <t>1,34; 7,82</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>7,36; 17,72</t>
+          <t>7,14; 17,76</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,6; 11,28</t>
+          <t>5,44; 11,29</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>8,04; 13,35</t>
+          <t>7,99; 13,35</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,55; 11,73</t>
+          <t>6,59; 11,34</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10,58; 21,31</t>
+          <t>11,17; 22,18</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,48; 10,45</t>
+          <t>5,48; 10,57</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,28; 13,49</t>
+          <t>8,39; 13,91</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,06; 16,32</t>
+          <t>10,07; 16,23</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>14,06; 22,84</t>
+          <t>14,48; 23,13</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>6,06; 9,99</t>
+          <t>6,1; 9,8</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9,0; 12,88</t>
+          <t>9,03; 12,74</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9,04; 13,14</t>
+          <t>9,12; 13,0</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>13,46; 20,97</t>
+          <t>13,73; 20,86</t>
         </is>
       </c>
     </row>
@@ -1638,4 +1639,1622 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Adultos que perciben algun tipo de pensión (tasa de respuesta: 99,16%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>2675</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1372</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1153</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1276</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>1374</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>4352</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>5251</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>4675</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>2747</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>5505</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>6528</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>862; 6087</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4228</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4170</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4331</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>595; 4960</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4275</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>1609; 8751</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>1636; 10571</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>2070; 8758</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>722; 6681</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>2226; 10136</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>2511; 11776</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>1319</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2940</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>4469</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2706</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>483</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>4596</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>5882</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>3645</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>1802</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>7536</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>10350</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>6351</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3962</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>753; 7217</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>1794; 8522</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>733; 6136</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2595</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>1886; 8607</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>2722; 10678</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>1306; 7360</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>481; 4779</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>4009; 12734</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>6064; 15882</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>3045; 11202</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>2417</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>4564</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>4358</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>4330</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>4787</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>4913</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>4188</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>5601</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>7205</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>9477</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>8546</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>9931</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>657; 5922</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2049; 8696</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1905; 7625</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>1716; 7678</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>2104; 9519</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>2022; 9398</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>1553; 8138</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>2381; 9484</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>4000; 12348</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>5260; 15042</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>5041; 13923</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>6037; 15295</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>4910</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>15376</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>11892</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>8228</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>6389</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>15516</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>15499</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>7853</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>11299</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>30891</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>27391</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>16081</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>2258; 9443</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>10009; 21940</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>7594; 17846</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>3097; 15388</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>3270; 11803</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>10043; 22383</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>9775; 21236</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>4015; 13819</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>6762; 17566</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>23107; 40141</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>20415; 36270</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>8809; 23809</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>3868</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>9999</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>6021</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>16626</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>2776</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>9795</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>9263</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>16580</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>6643</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>19793</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>15284</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>33207</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>1352; 7762</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>6069; 15698</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>3123; 10484</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>10749; 24587</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>697; 6390</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>5429; 15842</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>5035; 14734</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>11288; 23143</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>3361; 12275</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>13377; 28191</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>10331; 22058</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>24919; 43408</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>5458</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>2687</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>659</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>8231</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>5092</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>4958</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>3891</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>7052</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>10550</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>7645</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>4550</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>15283</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>2624; 10407</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>671; 6150</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3363</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>4023; 14095</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>2085; 9632</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>2310; 9252</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>1378; 8380</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>3207; 12097</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>6285; 15816</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>4010; 12187</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>1608; 9355</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>9480; 23590</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>20646</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>36937</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>28552</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>41397</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>21527</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>41152</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>43074</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>45984</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>42174</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>78089</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>71626</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>87381</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>14117; 29273</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>28078; 46899</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>21436; 36896</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>28719; 57023</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>15244; 29423</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>31702; 52562</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>33439; 53888</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>36394; 58139</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>32779; 52699</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>65864; 92866</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>59976; 85512</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>69789; 106073</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP36A-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP36A-Clase-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,35; 37,76</t>
+          <t>5,7; 36,42</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,98</t>
+          <t>0,0; 20,89</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,66</t>
+          <t>0,0; 20,58</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,09</t>
+          <t>0,0; 30,23</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,3; 27,46</t>
+          <t>3,32; 29,22</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,16</t>
+          <t>0,0; 21,06</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,54; 41,02</t>
+          <t>7,25; 39,47</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,4; 47,84</t>
+          <t>6,49; 45,29</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,06; 25,62</t>
+          <t>6,2; 26,09</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,7; 15,73</t>
+          <t>1,69; 16,12</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5,71; 26,02</t>
+          <t>6,1; 26,64</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6,79; 31,84</t>
+          <t>7,11; 33,64</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,5</t>
+          <t>0,0; 17,55</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,04; 19,57</t>
+          <t>2,0; 17,71</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,44; 21,11</t>
+          <t>4,97; 21,89</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,75; 31,42</t>
+          <t>3,78; 31,6</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,83</t>
+          <t>0,0; 11,24</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,74; 21,62</t>
+          <t>4,76; 22,25</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,94; 27,24</t>
+          <t>7,29; 27,58</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,27; 40,96</t>
+          <t>7,72; 40,8</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,01; 10,06</t>
+          <t>1,01; 10,61</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5,23; 16,6</t>
+          <t>5,37; 16,95</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7,62; 19,96</t>
+          <t>7,52; 20,35</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,12; 29,87</t>
+          <t>8,67; 30,94</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,87; 34,83</t>
+          <t>3,92; 36,23</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,68; 28,36</t>
+          <t>6,51; 27,07</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,61; 34,46</t>
+          <t>8,24; 34,93</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12,57; 56,21</t>
+          <t>12,5; 56,03</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,91; 31,25</t>
+          <t>7,05; 29,55</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,94; 22,96</t>
+          <t>5,33; 22,61</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,74; 30,07</t>
+          <t>6,65; 31,53</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13,48; 53,7</t>
+          <t>13,82; 54,04</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8,43; 26,02</t>
+          <t>7,9; 25,78</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7,35; 21,01</t>
+          <t>7,92; 20,73</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10,25; 28,3</t>
+          <t>10,43; 28,25</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>19,27; 48,83</t>
+          <t>16,92; 45,08</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,08; 12,86</t>
+          <t>3,14; 14,02</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,46; 18,55</t>
+          <t>8,8; 19,08</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,96; 16,35</t>
+          <t>6,99; 16,32</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,34; 16,57</t>
+          <t>2,93; 15,82</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,23; 15,27</t>
+          <t>4,12; 14,29</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,24; 18,35</t>
+          <t>8,3; 18,07</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,25; 22,27</t>
+          <t>10,72; 23,53</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,88; 20,25</t>
+          <t>6,26; 20,34</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,49; 11,65</t>
+          <t>4,57; 11,42</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9,62; 16,71</t>
+          <t>9,73; 17,24</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9,98; 17,74</t>
+          <t>10,09; 17,71</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,47; 14,78</t>
+          <t>5,02; 14,8</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,37; 13,59</t>
+          <t>2,92; 14,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,32; 16,34</t>
+          <t>6,26; 16,93</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,83; 12,85</t>
+          <t>3,78; 12,69</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21,14; 48,35</t>
+          <t>21,96; 48,05</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,16; 10,64</t>
+          <t>1,32; 10,41</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,0; 17,49</t>
+          <t>6,39; 17,41</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,99; 17,53</t>
+          <t>6,5; 17,77</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>19,51; 40,01</t>
+          <t>18,91; 39,1</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,87; 10,47</t>
+          <t>2,79; 10,0</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7,17; 15,11</t>
+          <t>7,34; 14,5</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6,24; 13,32</t>
+          <t>5,91; 13,39</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>22,93; 39,94</t>
+          <t>23,2; 39,98</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,74; 14,85</t>
+          <t>3,83; 15,35</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,42; 13,04</t>
+          <t>1,43; 13,33</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,16</t>
+          <t>0,0; 7,58</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6,16; 21,58</t>
+          <t>6,33; 23,38</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,96; 13,68</t>
+          <t>2,75; 12,62</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,59; 14,38</t>
+          <t>3,43; 14,22</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,12; 12,88</t>
+          <t>2,43; 12,8</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4,75; 17,92</t>
+          <t>5,43; 19,04</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4,47; 11,26</t>
+          <t>4,58; 12,09</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3,6; 10,93</t>
+          <t>3,68; 11,39</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1,34; 7,82</t>
+          <t>1,62; 7,68</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>7,14; 17,76</t>
+          <t>7,09; 17,47</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,44; 11,29</t>
+          <t>5,49; 10,97</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,99; 13,35</t>
+          <t>8,15; 13,34</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,59; 11,34</t>
+          <t>6,37; 11,44</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11,17; 22,18</t>
+          <t>11,04; 21,52</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,48; 10,57</t>
+          <t>5,5; 10,19</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,39; 13,91</t>
+          <t>8,5; 13,57</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,07; 16,23</t>
+          <t>10,2; 16,29</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>14,48; 23,13</t>
+          <t>14,08; 23,23</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>6,1; 9,8</t>
+          <t>6,04; 9,9</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9,03; 12,74</t>
+          <t>8,84; 12,54</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9,12; 13,0</t>
+          <t>8,92; 12,98</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>13,73; 20,86</t>
+          <t>13,62; 20,68</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>862; 6087</t>
+          <t>920; 5871</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 4228</t>
+          <t>0; 4654</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 4170</t>
+          <t>0; 3627</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 4331</t>
+          <t>0; 4500</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>595; 4960</t>
+          <t>600; 5278</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 4275</t>
+          <t>0; 4255</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1609; 8751</t>
+          <t>1546; 8422</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1636; 10571</t>
+          <t>1434; 10008</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2070; 8758</t>
+          <t>2118; 8918</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>722; 6681</t>
+          <t>719; 6850</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2226; 10136</t>
+          <t>2377; 10380</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2511; 11776</t>
+          <t>2630; 12442</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3962</t>
+          <t>0; 4484</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>753; 7217</t>
+          <t>736; 6534</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1794; 8522</t>
+          <t>2006; 8838</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>733; 6136</t>
+          <t>739; 6171</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 2595</t>
+          <t>0; 2466</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1886; 8607</t>
+          <t>1896; 8857</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2722; 10678</t>
+          <t>2857; 10812</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1306; 7360</t>
+          <t>1388; 7331</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>481; 4779</t>
+          <t>481; 5037</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4009; 12734</t>
+          <t>4119; 12997</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6064; 15882</t>
+          <t>5985; 16193</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3045; 11202</t>
+          <t>3251; 11602</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>657; 5922</t>
+          <t>667; 6159</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2049; 8696</t>
+          <t>1998; 8301</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1905; 7625</t>
+          <t>1824; 7730</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1716; 7678</t>
+          <t>1708; 7654</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2104; 9519</t>
+          <t>2146; 8999</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2022; 9398</t>
+          <t>2183; 9255</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1553; 8138</t>
+          <t>1798; 8534</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2381; 9484</t>
+          <t>2441; 9544</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4000; 12348</t>
+          <t>3749; 12235</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5260; 15042</t>
+          <t>5674; 14843</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5041; 13923</t>
+          <t>5130; 13897</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6037; 15295</t>
+          <t>5300; 14121</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2258; 9443</t>
+          <t>2309; 10295</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10009; 21940</t>
+          <t>10407; 22566</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7594; 17846</t>
+          <t>7626; 17809</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3097; 15388</t>
+          <t>2720; 14683</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3270; 11803</t>
+          <t>3184; 11046</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10043; 22383</t>
+          <t>10123; 22032</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9775; 21236</t>
+          <t>10220; 22434</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4015; 13819</t>
+          <t>4275; 13881</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6762; 17566</t>
+          <t>6886; 17214</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>23107; 40141</t>
+          <t>23376; 41416</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>20415; 36270</t>
+          <t>20631; 36209</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>8809; 23809</t>
+          <t>8093; 23832</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1352; 7762</t>
+          <t>1667; 7995</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>6069; 15698</t>
+          <t>6017; 16263</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3123; 10484</t>
+          <t>3082; 10353</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10749; 24587</t>
+          <t>11167; 24437</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>697; 6390</t>
+          <t>794; 6251</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5429; 15842</t>
+          <t>5782; 15762</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5035; 14734</t>
+          <t>5468; 14935</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>11288; 23143</t>
+          <t>10940; 22613</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3361; 12275</t>
+          <t>3268; 11721</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>13377; 28191</t>
+          <t>13706; 27065</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>10331; 22058</t>
+          <t>9791; 22175</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>24919; 43408</t>
+          <t>25221; 43461</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2624; 10407</t>
+          <t>2687; 10758</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>671; 6150</t>
+          <t>676; 6287</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 3363</t>
+          <t>0; 4135</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4023; 14095</t>
+          <t>4132; 15272</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2085; 9632</t>
+          <t>1936; 8886</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2310; 9252</t>
+          <t>2209; 9150</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1378; 8380</t>
+          <t>1581; 8333</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>3207; 12097</t>
+          <t>3663; 12857</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>6285; 15816</t>
+          <t>6436; 16994</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>4010; 12187</t>
+          <t>4109; 12703</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1608; 9355</t>
+          <t>1940; 9189</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>9480; 23590</t>
+          <t>9422; 23205</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>14117; 29273</t>
+          <t>14245; 28448</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>28078; 46899</t>
+          <t>28632; 46856</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>21436; 36896</t>
+          <t>20731; 37222</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>28719; 57023</t>
+          <t>28373; 55325</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>15244; 29423</t>
+          <t>15298; 28357</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>31702; 52562</t>
+          <t>32100; 51266</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>33439; 53888</t>
+          <t>33881; 54111</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>36394; 58139</t>
+          <t>35376; 58387</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>32779; 52699</t>
+          <t>32497; 53213</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>65864; 92866</t>
+          <t>64482; 91443</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>59976; 85512</t>
+          <t>58655; 85346</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>69789; 106073</t>
+          <t>69229; 105111</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP36A-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP36A-Clase-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>11,07%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6,8%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>20,4%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>31,62%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>16,59%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>6,16%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>6,54%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>8,57%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>11,07%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>6,8%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>20,4%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>22,59%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,7; 36,42</t>
+          <t>3,33; 30,06</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,89</t>
+          <t>0,0; 20,91</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,58</t>
+          <t>8,12; 40,35</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,23</t>
+          <t>13,62; 56,17</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,32; 29,22</t>
+          <t>5,18; 37,14</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,06</t>
+          <t>0,0; 20,59</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,25; 39,47</t>
+          <t>0,0; 23,81</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,49; 45,29</t>
+          <t>0,0; 32,32</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,2; 26,09</t>
+          <t>5,77; 24,71</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,69; 16,12</t>
+          <t>1,71; 15,42</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6,1; 26,64</t>
+          <t>6,1; 25,89</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7,11; 33,64</t>
+          <t>12,45; 40,74</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>2,2%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>11,55%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>15,0%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>20,49%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>5,16%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>7,97%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>11,07%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>13,86%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>2,2%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>11,55%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>15,0%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>17,27%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,55</t>
+          <t>0,0; 12,28</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,0; 17,71</t>
+          <t>4,68; 21,66</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,97; 21,89</t>
+          <t>6,92; 26,45</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,78; 31,6</t>
+          <t>7,16; 41,1</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,24</t>
+          <t>0,0; 17,97</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,76; 22,25</t>
+          <t>2,01; 19,83</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,29; 27,58</t>
+          <t>4,49; 21,04</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,72; 40,8</t>
+          <t>4,07; 33,31</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,01; 10,61</t>
+          <t>1,02; 9,64</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5,37; 16,95</t>
+          <t>5,38; 16,19</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7,52; 20,35</t>
+          <t>7,46; 21,04</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,67; 30,94</t>
+          <t>8,14; 30,15</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>15,72%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>12,0%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>15,47%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>32,2%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>14,22%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>14,88%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>19,69%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>31,7%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>15,72%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>12,0%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>15,47%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>34,56%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>31,71%</t>
+          <t>33,29%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,92; 36,23</t>
+          <t>6,89; 29,78</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,51; 27,07</t>
+          <t>4,74; 21,11</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,24; 34,93</t>
+          <t>5,75; 29,65</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12,5; 56,03</t>
+          <t>14,26; 57,88</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,05; 29,55</t>
+          <t>3,87; 36,33</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,33; 22,61</t>
+          <t>6,5; 27,28</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,65; 31,53</t>
+          <t>8,66; 34,6</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13,82; 54,04</t>
+          <t>12,57; 57,07</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7,9; 25,78</t>
+          <t>7,44; 25,62</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7,92; 20,73</t>
+          <t>7,53; 20,56</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10,43; 28,25</t>
+          <t>10,06; 26,91</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>16,92; 45,08</t>
+          <t>18,38; 49,8</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>8,26%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>12,72%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>16,26%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>12,14%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>6,69%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>13,0%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>10,89%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>8,86%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>8,26%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>12,72%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>16,26%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>12,89%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,14; 14,02</t>
+          <t>4,3; 14,35</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,8; 19,08</t>
+          <t>8,19; 18,55</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,99; 16,32</t>
+          <t>10,41; 22,71</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,93; 15,82</t>
+          <t>6,5; 20,33</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,12; 14,29</t>
+          <t>2,83; 13,02</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,3; 18,07</t>
+          <t>8,87; 19,42</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,72; 23,53</t>
+          <t>7,16; 16,57</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,26; 20,34</t>
+          <t>7,79; 23,42</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,57; 11,42</t>
+          <t>4,37; 11,35</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9,73; 17,24</t>
+          <t>9,7; 17,11</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10,09; 17,71</t>
+          <t>9,88; 17,37</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,02; 14,8</t>
+          <t>8,21; 18,95</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>4,62%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>10,82%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>11,02%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>28,91%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>6,77%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>10,41%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>7,38%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>32,69%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>4,62%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>10,82%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>11,02%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>30,55%</t>
+          <t>28,53%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,92; 14,0</t>
+          <t>1,17; 11,29</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,26; 16,93</t>
+          <t>6,4; 16,56</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,78; 12,69</t>
+          <t>6,56; 17,82</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21,96; 48,05</t>
+          <t>19,33; 40,98</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,32; 10,41</t>
+          <t>3,2; 13,72</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,39; 17,41</t>
+          <t>6,0; 16,12</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,5; 17,77</t>
+          <t>4,09; 13,66</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>18,91; 39,1</t>
+          <t>19,38; 39,72</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,79; 10,0</t>
+          <t>2,88; 10,27</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7,34; 14,5</t>
+          <t>7,21; 14,27</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5,91; 13,39</t>
+          <t>6,24; 13,44</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>23,2; 39,98</t>
+          <t>21,64; 36,73</t>
         </is>
       </c>
     </row>
@@ -1349,42 +1349,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>7,23%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>7,7%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>5,98%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>9,97%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>7,79%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>5,7%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>1,21%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>12,6%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>7,23%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>7,7%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>5,98%</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,58%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,83; 15,35</t>
+          <t>3,27; 12,65</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,43; 13,33</t>
+          <t>3,5; 14,85</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,58</t>
+          <t>2,2; 12,81</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6,33; 23,38</t>
+          <t>4,34; 17,8</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,75; 12,62</t>
+          <t>3,81; 14,41</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,43; 14,22</t>
+          <t>1,43; 14,24</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,43; 12,8</t>
+          <t>0,0; 6,82</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5,43; 19,04</t>
+          <t>6,46; 24,5</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4,58; 12,09</t>
+          <t>4,58; 11,86</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3,68; 11,39</t>
+          <t>3,54; 11,45</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1,62; 7,68</t>
+          <t>1,32; 7,63</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>7,09; 17,47</t>
+          <t>7,18; 18,32</t>
         </is>
       </c>
     </row>
@@ -1489,62 +1489,62 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>7,74%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>10,89%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>12,97%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>18,9%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>7,96%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>10,51%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>8,77%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>16,1%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>7,74%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>17,94%</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>7,85%</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>10,71%</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
         <is>
           <t>10,89%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>12,97%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>18,3%</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>7,85%</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>10,71%</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>10,89%</t>
-        </is>
-      </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>18,43%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,49; 10,97</t>
+          <t>5,48; 10,45</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>8,15; 13,34</t>
+          <t>8,28; 13,49</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,37; 11,44</t>
+          <t>10,06; 16,32</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11,04; 21,52</t>
+          <t>14,54; 24,01</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,5; 10,19</t>
+          <t>5,6; 11,28</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,5; 13,57</t>
+          <t>8,04; 13,35</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,2; 16,29</t>
+          <t>6,55; 11,73</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>14,08; 23,23</t>
+          <t>13,72; 23,0</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>6,04; 9,9</t>
+          <t>6,06; 9,99</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8,84; 12,54</t>
+          <t>9,0; 12,88</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8,92; 12,98</t>
+          <t>9,04; 13,14</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>13,62; 20,68</t>
+          <t>14,97; 21,87</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1683,7 +1683,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1791,42 +1791,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1859,42 +1859,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1374</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>4352</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>5215</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>2675</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>1372</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>1153</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>1276</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>1374</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>4352</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5251</t>
+          <t>1387</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6528</t>
+          <t>6602</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>920; 5871</t>
+          <t>602; 5430</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 4654</t>
+          <t>0; 4224</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 3627</t>
+          <t>1731; 8608</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 4500</t>
+          <t>2246; 9264</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>600; 5278</t>
+          <t>834; 5988</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 4255</t>
+          <t>0; 4589</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1546; 8422</t>
+          <t>0; 4197</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1434; 10008</t>
+          <t>0; 4115</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2118; 8918</t>
+          <t>1973; 8447</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>719; 6850</t>
+          <t>726; 6550</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2377; 10380</t>
+          <t>2376; 10086</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2630; 12442</t>
+          <t>3637; 11907</t>
         </is>
       </c>
     </row>
@@ -1999,42 +1999,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2067,42 +2067,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>483</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>4596</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>5882</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>3567</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>1319</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>2940</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>4469</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2706</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>483</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>4596</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>5882</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>3645</t>
+          <t>2870</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6351</t>
+          <t>6436</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 4484</t>
+          <t>0; 2695</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>736; 6534</t>
+          <t>1864; 8621</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2006; 8838</t>
+          <t>2713; 10367</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>739; 6171</t>
+          <t>1246; 7152</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 2466</t>
+          <t>0; 4592</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1896; 8857</t>
+          <t>741; 7315</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2857; 10812</t>
+          <t>1814; 8493</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1388; 7331</t>
+          <t>807; 6615</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>481; 5037</t>
+          <t>484; 4576</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4119; 12997</t>
+          <t>4126; 12419</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5985; 16193</t>
+          <t>5934; 16741</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3251; 11602</t>
+          <t>3033; 11235</t>
         </is>
       </c>
     </row>
@@ -2207,42 +2207,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2275,42 +2275,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>4787</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>4913</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>4188</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>5223</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>2417</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>4564</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>4358</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>4330</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>4787</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>4913</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>4188</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5601</t>
+          <t>4853</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9931</t>
+          <t>10076</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>667; 6159</t>
+          <t>2098; 9070</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1998; 8301</t>
+          <t>1941; 8643</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1824; 7730</t>
+          <t>1557; 8025</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1708; 7654</t>
+          <t>2313; 9388</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2146; 8999</t>
+          <t>658; 6176</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2183; 9255</t>
+          <t>1994; 8366</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1798; 8534</t>
+          <t>1916; 7657</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2441; 9544</t>
+          <t>1765; 8014</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3749; 12235</t>
+          <t>3530; 12161</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5674; 14843</t>
+          <t>5395; 14720</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5130; 13897</t>
+          <t>4947; 13237</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5300; 14121</t>
+          <t>5562; 15071</t>
         </is>
       </c>
     </row>
@@ -2415,42 +2415,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>13</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2483,42 +2483,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>6389</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>15516</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>15499</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>7525</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>4910</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>15376</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>11892</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>8228</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>6389</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>15516</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>15499</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>7853</t>
+          <t>8205</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>16081</t>
+          <t>15730</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2309; 10295</t>
+          <t>3324; 11097</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10407; 22566</t>
+          <t>9986; 22622</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7626; 17809</t>
+          <t>9928; 21652</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2720; 14683</t>
+          <t>4025; 12599</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3184; 11046</t>
+          <t>2077; 9560</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10123; 22032</t>
+          <t>10487; 22975</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10220; 22434</t>
+          <t>7815; 18088</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4275; 13881</t>
+          <t>4677; 14066</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6886; 17214</t>
+          <t>6593; 17107</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>23376; 41416</t>
+          <t>23305; 41118</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>20631; 36209</t>
+          <t>20212; 35512</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>8093; 23832</t>
+          <t>10016; 23124</t>
         </is>
       </c>
     </row>
@@ -2623,42 +2623,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>21</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2691,42 +2691,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>2776</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>9795</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>9263</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>15609</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>3868</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>9999</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>6021</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>16626</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>2776</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>9795</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>9263</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>16580</t>
+          <t>13881</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>33207</t>
+          <t>29490</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1667; 7995</t>
+          <t>703; 6783</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>6017; 16263</t>
+          <t>5799; 14996</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3082; 10353</t>
+          <t>5511; 14980</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>11167; 24437</t>
+          <t>10435; 22125</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>794; 6251</t>
+          <t>1827; 7837</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5782; 15762</t>
+          <t>5761; 15484</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5468; 14935</t>
+          <t>3339; 11148</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>10940; 22613</t>
+          <t>9572; 19618</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3268; 11721</t>
+          <t>3378; 12034</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>13706; 27065</t>
+          <t>13449; 26637</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>9791; 22175</t>
+          <t>10333; 22263</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>25221; 43461</t>
+          <t>22366; 37971</t>
         </is>
       </c>
     </row>
@@ -2836,37 +2836,37 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>10</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -2899,42 +2899,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>5092</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>4958</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>3891</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>6409</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>5458</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>2687</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>659</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>8231</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>5092</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>4958</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>3891</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>7052</t>
+          <t>8741</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>15283</t>
+          <t>15149</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2687; 10758</t>
+          <t>2301; 8908</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>676; 6287</t>
+          <t>2254; 9558</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 4135</t>
+          <t>1432; 8340</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4132; 15272</t>
+          <t>2791; 11445</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1936; 8886</t>
+          <t>2671; 10104</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2209; 9150</t>
+          <t>673; 6716</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1581; 8333</t>
+          <t>0; 3724</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>3663; 12857</t>
+          <t>4301; 16313</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>6436; 16994</t>
+          <t>6434; 16659</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>4109; 12703</t>
+          <t>3944; 12767</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1940; 9189</t>
+          <t>1584; 9131</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>9422; 23205</t>
+          <t>9400; 23967</t>
         </is>
       </c>
     </row>
@@ -3039,42 +3039,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>56</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3107,42 +3107,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>21527</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>41152</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>43074</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>43547</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>20646</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>36937</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>28552</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>41397</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>21527</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>41152</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>43074</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>45984</t>
+          <t>39937</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>87381</t>
+          <t>83484</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>14245; 28448</t>
+          <t>15250; 29085</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>28632; 46856</t>
+          <t>31273; 50983</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>20731; 37222</t>
+          <t>33422; 54207</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>28373; 55325</t>
+          <t>33497; 55304</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>15298; 28357</t>
+          <t>14518; 29246</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>32100; 51266</t>
+          <t>28242; 46897</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>33881; 54111</t>
+          <t>21330; 38190</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>35376; 58387</t>
+          <t>30548; 51215</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>32497; 53213</t>
+          <t>32588; 53721</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>64482; 91443</t>
+          <t>65594; 93916</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>58655; 85346</t>
+          <t>59432; 86407</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>69229; 105111</t>
+          <t>67826; 99069</t>
         </is>
       </c>
     </row>
